--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/199.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/199.xlsx
@@ -426,13 +426,13 @@
         <v>-14.71937455587983</v>
       </c>
       <c r="E2">
-        <v>-13.22031135437624</v>
+        <v>-17.91811859061542</v>
       </c>
       <c r="F2">
-        <v>9.635021461940333</v>
+        <v>9.649296987062105</v>
       </c>
       <c r="G2">
-        <v>-14.36792769729117</v>
+        <v>-18.33328590204804</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.33137093742011</v>
       </c>
       <c r="E3">
-        <v>-13.45984498701197</v>
+        <v>-18.42771682764658</v>
       </c>
       <c r="F3">
-        <v>9.797211952152319</v>
+        <v>10.01565726018663</v>
       </c>
       <c r="G3">
-        <v>-13.44965519669921</v>
+        <v>-17.71705930009533</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.87492702405381</v>
       </c>
       <c r="E4">
-        <v>-12.70339057487468</v>
+        <v>-19.49995531776074</v>
       </c>
       <c r="F4">
-        <v>9.691157501818999</v>
+        <v>9.592467283992475</v>
       </c>
       <c r="G4">
-        <v>-13.94253418240421</v>
+        <v>-16.71866001054362</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.37665071103331</v>
       </c>
       <c r="E5">
-        <v>-12.92599677166973</v>
+        <v>-17.48355716789136</v>
       </c>
       <c r="F5">
-        <v>9.872338209663019</v>
+        <v>9.732728198393371</v>
       </c>
       <c r="G5">
-        <v>-12.13028361966023</v>
+        <v>-16.25442055429885</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.83532136359244</v>
       </c>
       <c r="E6">
-        <v>-13.45022650821968</v>
+        <v>-19.99505790949335</v>
       </c>
       <c r="F6">
-        <v>9.921040333974613</v>
+        <v>9.490920060694497</v>
       </c>
       <c r="G6">
-        <v>-10.88947128826815</v>
+        <v>-14.95358968755256</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.26059929197283</v>
       </c>
       <c r="E7">
-        <v>-13.77250441792355</v>
+        <v>-20.24024307769065</v>
       </c>
       <c r="F7">
-        <v>9.768174704192736</v>
+        <v>10.11515991914777</v>
       </c>
       <c r="G7">
-        <v>-10.93746095640542</v>
+        <v>-14.78080238422138</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.65211559020061</v>
       </c>
       <c r="E8">
-        <v>-15.83744780915517</v>
+        <v>-21.65083556023592</v>
       </c>
       <c r="F8">
-        <v>9.812868468832352</v>
+        <v>10.56461882536132</v>
       </c>
       <c r="G8">
-        <v>-9.015070198842656</v>
+        <v>-14.86652565041526</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.01426377550407</v>
       </c>
       <c r="E9">
-        <v>-15.00717474221884</v>
+        <v>-22.42211166780031</v>
       </c>
       <c r="F9">
-        <v>9.515941030452526</v>
+        <v>10.14647453621376</v>
       </c>
       <c r="G9">
-        <v>-7.768318748753128</v>
+        <v>-11.52351359104044</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.35841389788729</v>
       </c>
       <c r="E10">
-        <v>-16.72135159376433</v>
+        <v>-21.27331026763846</v>
       </c>
       <c r="F10">
-        <v>9.757071342019589</v>
+        <v>10.07591251915135</v>
       </c>
       <c r="G10">
-        <v>-8.255680710316936</v>
+        <v>-12.3360737514724</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.696438745704869</v>
       </c>
       <c r="E11">
-        <v>-17.22395786692764</v>
+        <v>-25.26645977744009</v>
       </c>
       <c r="F11">
-        <v>10.25222966612906</v>
+        <v>10.66193121904141</v>
       </c>
       <c r="G11">
-        <v>-6.920762811425536</v>
+        <v>-11.69784029804739</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.039487419630145</v>
       </c>
       <c r="E12">
-        <v>-17.68173677588904</v>
+        <v>-23.72317394952206</v>
       </c>
       <c r="F12">
-        <v>10.50338325243494</v>
+        <v>10.70010169901533</v>
       </c>
       <c r="G12">
-        <v>-7.801156049957158</v>
+        <v>-10.99922249398607</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.396486086758962</v>
       </c>
       <c r="E13">
-        <v>-18.07464982316455</v>
+        <v>-22.69848896496244</v>
       </c>
       <c r="F13">
-        <v>10.43986080816666</v>
+        <v>10.83307598249929</v>
       </c>
       <c r="G13">
-        <v>-6.43984317148115</v>
+        <v>-10.40599921771298</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.790756863819778</v>
       </c>
       <c r="E14">
-        <v>-20.03722705945278</v>
+        <v>-24.33676406366536</v>
       </c>
       <c r="F14">
-        <v>10.78049061128304</v>
+        <v>10.52208840300219</v>
       </c>
       <c r="G14">
-        <v>-6.416321745424628</v>
+        <v>-9.330542014916425</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.239838525121711</v>
       </c>
       <c r="E15">
-        <v>-20.36979819057609</v>
+        <v>-23.45184137240447</v>
       </c>
       <c r="F15">
-        <v>10.66251719023012</v>
+        <v>11.01903631479611</v>
       </c>
       <c r="G15">
-        <v>-4.364107944539341</v>
+        <v>-8.879797997562497</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.757247293392463</v>
       </c>
       <c r="E16">
-        <v>-21.48788748001792</v>
+        <v>-25.95432139378319</v>
       </c>
       <c r="F16">
-        <v>11.53141585703006</v>
+        <v>10.83617846238764</v>
       </c>
       <c r="G16">
-        <v>-4.54734995068354</v>
+        <v>-8.464403985476904</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.348124965135773</v>
       </c>
       <c r="E17">
-        <v>-22.61754702054934</v>
+        <v>-27.44872234478841</v>
       </c>
       <c r="F17">
-        <v>11.28460954346206</v>
+        <v>11.69546086686903</v>
       </c>
       <c r="G17">
-        <v>-5.443776161261852</v>
+        <v>-8.641501619100216</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.021776674210587</v>
       </c>
       <c r="E18">
-        <v>-22.42280452432349</v>
+        <v>-27.85341848143189</v>
       </c>
       <c r="F18">
-        <v>11.67777562291131</v>
+        <v>11.05864479974125</v>
       </c>
       <c r="G18">
-        <v>-3.792926280466725</v>
+        <v>-8.663006922923323</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.780525325633924</v>
       </c>
       <c r="E19">
-        <v>-24.96471396888699</v>
+        <v>-29.91557912538579</v>
       </c>
       <c r="F19">
-        <v>11.87170199596279</v>
+        <v>11.58135168824978</v>
       </c>
       <c r="G19">
-        <v>-4.492593527463995</v>
+        <v>-7.66741663126168</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.62198480872579</v>
       </c>
       <c r="E20">
-        <v>-25.32407555223968</v>
+        <v>-29.56333177469915</v>
       </c>
       <c r="F20">
-        <v>11.92601360662687</v>
+        <v>12.1744131283458</v>
       </c>
       <c r="G20">
-        <v>-4.124321820584389</v>
+        <v>-9.009525035064376</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.537936096961217</v>
       </c>
       <c r="E21">
-        <v>-25.38321289430584</v>
+        <v>-32.03564083800177</v>
       </c>
       <c r="F21">
-        <v>12.47809507245498</v>
+        <v>11.89867725882047</v>
       </c>
       <c r="G21">
-        <v>-3.76179059966988</v>
+        <v>-7.152037522799021</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.522484874389335</v>
       </c>
       <c r="E22">
-        <v>-26.5112421841945</v>
+        <v>-31.64388934430922</v>
       </c>
       <c r="F22">
-        <v>12.37440826246524</v>
+        <v>12.04090196855651</v>
       </c>
       <c r="G22">
-        <v>-3.824767107463436</v>
+        <v>-5.410687258596838</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.568167727790279</v>
       </c>
       <c r="E23">
-        <v>-25.89455006535595</v>
+        <v>-30.2022768148114</v>
       </c>
       <c r="F23">
-        <v>12.31480232292584</v>
+        <v>11.98641931765356</v>
       </c>
       <c r="G23">
-        <v>-2.994104884022745</v>
+        <v>-7.189363923754303</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.666620774388599</v>
       </c>
       <c r="E24">
-        <v>-25.29685942345358</v>
+        <v>-31.92988512026364</v>
       </c>
       <c r="F24">
-        <v>12.73370362350099</v>
+        <v>12.25432059401521</v>
       </c>
       <c r="G24">
-        <v>-2.701045461249842</v>
+        <v>-6.921166697981327</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.805462283390253</v>
       </c>
       <c r="E25">
-        <v>-25.95193941645515</v>
+        <v>-31.74964959052135</v>
       </c>
       <c r="F25">
-        <v>12.32697943770966</v>
+        <v>12.7069738350602</v>
       </c>
       <c r="G25">
-        <v>-2.014660122956129</v>
+        <v>-5.896774660128026</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.972676233871294</v>
       </c>
       <c r="E26">
-        <v>-27.53314668571342</v>
+        <v>-32.59547796567402</v>
       </c>
       <c r="F26">
-        <v>12.21198021636594</v>
+        <v>12.13317342630776</v>
       </c>
       <c r="G26">
-        <v>-2.407168333728739</v>
+        <v>-5.483707961556542</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.156333661739942</v>
       </c>
       <c r="E27">
-        <v>-27.68439318909559</v>
+        <v>-32.03204296540267</v>
       </c>
       <c r="F27">
-        <v>12.38953898878135</v>
+        <v>12.24398216179922</v>
       </c>
       <c r="G27">
-        <v>-2.310152796700397</v>
+        <v>-5.996660440138916</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.34773626788528</v>
       </c>
       <c r="E28">
-        <v>-28.30450430580994</v>
+        <v>-32.467940287959</v>
       </c>
       <c r="F28">
-        <v>12.79630910204422</v>
+        <v>11.8950695767451</v>
       </c>
       <c r="G28">
-        <v>-2.090643764173481</v>
+        <v>-5.492960936338805</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.536710513428701</v>
       </c>
       <c r="E29">
-        <v>-27.96338341576015</v>
+        <v>-31.90117685929201</v>
       </c>
       <c r="F29">
-        <v>12.24780206046726</v>
+        <v>11.91462834480078</v>
       </c>
       <c r="G29">
-        <v>-2.138984350137919</v>
+        <v>-4.587427414981957</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.71332759152464</v>
       </c>
       <c r="E30">
-        <v>-27.3469901762061</v>
+        <v>-31.61567242276742</v>
       </c>
       <c r="F30">
-        <v>12.05823404609508</v>
+        <v>11.42717791738175</v>
       </c>
       <c r="G30">
-        <v>-2.255495689847029</v>
+        <v>-4.430037458953926</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.870311867535125</v>
       </c>
       <c r="E31">
-        <v>-28.93467769176933</v>
+        <v>-33.95388204951789</v>
       </c>
       <c r="F31">
-        <v>12.20137888896799</v>
+        <v>11.6272047256195</v>
       </c>
       <c r="G31">
-        <v>-3.226386001240169</v>
+        <v>-5.07004536478799</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.005929737202821</v>
       </c>
       <c r="E32">
-        <v>-28.20297139008397</v>
+        <v>-33.22904317866516</v>
       </c>
       <c r="F32">
-        <v>12.24617876190394</v>
+        <v>11.39961826704127</v>
       </c>
       <c r="G32">
-        <v>-3.043574366016075</v>
+        <v>-4.23715183365383</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.117495130034369</v>
       </c>
       <c r="E33">
-        <v>-27.93651597947264</v>
+        <v>-32.92824834965367</v>
       </c>
       <c r="F33">
-        <v>11.94621852669605</v>
+        <v>11.2729503005126</v>
       </c>
       <c r="G33">
-        <v>-2.320763095153761</v>
+        <v>-4.194495454380321</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.2009122086538</v>
       </c>
       <c r="E34">
-        <v>-27.34321795735771</v>
+        <v>-31.37578330492209</v>
       </c>
       <c r="F34">
-        <v>12.60317616565638</v>
+        <v>11.84033194918976</v>
       </c>
       <c r="G34">
-        <v>-1.700088775269041</v>
+        <v>-5.028848936097298</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.254516710388191</v>
       </c>
       <c r="E35">
-        <v>-27.43264626206119</v>
+        <v>-33.35508872419466</v>
       </c>
       <c r="F35">
-        <v>12.18852394805237</v>
+        <v>11.40800874098127</v>
       </c>
       <c r="G35">
-        <v>-2.453102153086126</v>
+        <v>-5.823224269882037</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.278827797530106</v>
       </c>
       <c r="E36">
-        <v>-26.68100561779405</v>
+        <v>-32.15639259741629</v>
       </c>
       <c r="F36">
-        <v>12.02379794466976</v>
+        <v>11.84348194025557</v>
       </c>
       <c r="G36">
-        <v>-2.561625146408975</v>
+        <v>-4.072088033065769</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.271856912765621</v>
       </c>
       <c r="E37">
-        <v>-26.69377591449568</v>
+        <v>-30.57267655355779</v>
       </c>
       <c r="F37">
-        <v>12.33762194146141</v>
+        <v>12.04339155425558</v>
       </c>
       <c r="G37">
-        <v>-2.811193932432473</v>
+        <v>-6.523904543814324</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.229091010138483</v>
       </c>
       <c r="E38">
-        <v>-26.25860767625459</v>
+        <v>-30.8237713803351</v>
       </c>
       <c r="F38">
-        <v>12.06105937744822</v>
+        <v>11.59177247317337</v>
       </c>
       <c r="G38">
-        <v>-2.426948843325884</v>
+        <v>-6.168709491814839</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.14867091302293</v>
       </c>
       <c r="E39">
-        <v>-24.89352635748641</v>
+        <v>-29.96602406159424</v>
       </c>
       <c r="F39">
-        <v>11.8117270529451</v>
+        <v>12.17645927638855</v>
       </c>
       <c r="G39">
-        <v>-3.642740071532149</v>
+        <v>-5.071051770631928</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.030743597311161</v>
       </c>
       <c r="E40">
-        <v>-23.65474870726616</v>
+        <v>-30.07747207116001</v>
       </c>
       <c r="F40">
-        <v>12.33380679391112</v>
+        <v>12.3960781105062</v>
       </c>
       <c r="G40">
-        <v>-3.383984521637174</v>
+        <v>-5.144271106323989</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.876274711742121</v>
       </c>
       <c r="E41">
-        <v>-25.09757486779803</v>
+        <v>-30.06588144193737</v>
       </c>
       <c r="F41">
-        <v>11.76708555060069</v>
+        <v>12.04063273855088</v>
       </c>
       <c r="G41">
-        <v>-1.887310057151445</v>
+        <v>-6.316008905039172</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.685646879681771</v>
       </c>
       <c r="E42">
-        <v>-22.8764081802498</v>
+        <v>-26.92124569237497</v>
       </c>
       <c r="F42">
-        <v>11.82795212004877</v>
+        <v>12.25419389754198</v>
       </c>
       <c r="G42">
-        <v>-3.103266812634673</v>
+        <v>-6.652499374741773</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.46364619753339</v>
       </c>
       <c r="E43">
-        <v>-22.64843121328165</v>
+        <v>-27.37552861940244</v>
       </c>
       <c r="F43">
-        <v>12.07279305457571</v>
+        <v>12.39285368526236</v>
       </c>
       <c r="G43">
-        <v>-2.770831761217678</v>
+        <v>-6.402106262878998</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.217001792339871</v>
       </c>
       <c r="E44">
-        <v>-21.64929587907331</v>
+        <v>-28.32821992418812</v>
       </c>
       <c r="F44">
-        <v>12.15610073684557</v>
+        <v>12.24618034560985</v>
       </c>
       <c r="G44">
-        <v>-3.545194847217524</v>
+        <v>-7.373181964822336</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.953795026249965</v>
       </c>
       <c r="E45">
-        <v>-22.75693797897944</v>
+        <v>-27.19864642466284</v>
       </c>
       <c r="F45">
-        <v>11.9759811119649</v>
+        <v>12.56780884515279</v>
       </c>
       <c r="G45">
-        <v>-3.559360671580065</v>
+        <v>-6.345585318887021</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.679823080215092</v>
       </c>
       <c r="E46">
-        <v>-22.00082773086674</v>
+        <v>-29.0800100080975</v>
       </c>
       <c r="F46">
-        <v>12.60428000867944</v>
+        <v>12.21792703207841</v>
       </c>
       <c r="G46">
-        <v>-2.131773981953387</v>
+        <v>-6.418698717121825</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.40214819006866</v>
       </c>
       <c r="E47">
-        <v>-21.19294796789834</v>
+        <v>-27.79364262453064</v>
       </c>
       <c r="F47">
-        <v>11.83889394421855</v>
+        <v>11.99830027943119</v>
       </c>
       <c r="G47">
-        <v>-3.112734972876989</v>
+        <v>-7.043094090192684</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.129675466330806</v>
       </c>
       <c r="E48">
-        <v>-20.6049527888464</v>
+        <v>-26.64892137944971</v>
       </c>
       <c r="F48">
-        <v>12.1644737900205</v>
+        <v>12.17122671204394</v>
       </c>
       <c r="G48">
-        <v>-2.303746891081907</v>
+        <v>-8.136865230912493</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.869845463930109</v>
       </c>
       <c r="E49">
-        <v>-19.26506337098288</v>
+        <v>-24.18969281331825</v>
       </c>
       <c r="F49">
-        <v>11.99690345081377</v>
+        <v>12.28207504018329</v>
       </c>
       <c r="G49">
-        <v>-2.890637093738364</v>
+        <v>-7.833576222423241</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.627150643241725</v>
       </c>
       <c r="E50">
-        <v>-21.0601459391494</v>
+        <v>-24.1171013749753</v>
       </c>
       <c r="F50">
-        <v>11.69113101489621</v>
+        <v>12.08467084894151</v>
       </c>
       <c r="G50">
-        <v>-3.171891111118226</v>
+        <v>-6.117018633764659</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.403576595156943</v>
       </c>
       <c r="E51">
-        <v>-18.58569717187817</v>
+        <v>-25.23602390363453</v>
       </c>
       <c r="F51">
-        <v>12.46678899592465</v>
+        <v>12.08758170041409</v>
       </c>
       <c r="G51">
-        <v>-3.73544527826836</v>
+        <v>-7.4455670430385</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.203573386700482</v>
       </c>
       <c r="E52">
-        <v>-19.52160595199141</v>
+        <v>-22.14948847559054</v>
       </c>
       <c r="F52">
-        <v>12.24254732423984</v>
+        <v>12.51241397964255</v>
       </c>
       <c r="G52">
-        <v>-3.915442949784074</v>
+        <v>-7.078695696922007</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.028486009725674</v>
       </c>
       <c r="E53">
-        <v>-17.7341448055798</v>
+        <v>-24.20498094156815</v>
       </c>
       <c r="F53">
-        <v>12.19872143044188</v>
+        <v>12.8744174777937</v>
       </c>
       <c r="G53">
-        <v>-3.835976614659408</v>
+        <v>-7.362829888921035</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.876571877242888</v>
       </c>
       <c r="E54">
-        <v>-18.47642509407308</v>
+        <v>-23.74717939023672</v>
       </c>
       <c r="F54">
-        <v>12.30129014405532</v>
+        <v>12.17941763903859</v>
       </c>
       <c r="G54">
-        <v>-2.391615390785243</v>
+        <v>-7.522682890830284</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.743065364031367</v>
       </c>
       <c r="E55">
-        <v>-18.15193728905346</v>
+        <v>-21.65437229843591</v>
       </c>
       <c r="F55">
-        <v>12.3162640834858</v>
+        <v>11.84448125868822</v>
       </c>
       <c r="G55">
-        <v>-2.626866067351393</v>
+        <v>-6.607356775768272</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.627209838118242</v>
       </c>
       <c r="E56">
-        <v>-16.20251526975752</v>
+        <v>-20.85033268142602</v>
       </c>
       <c r="F56">
-        <v>12.16257809403972</v>
+        <v>12.72271112074192</v>
       </c>
       <c r="G56">
-        <v>-3.44300823805684</v>
+        <v>-7.215255700416944</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.526427832345094</v>
       </c>
       <c r="E57">
-        <v>-16.12530025945273</v>
+        <v>-20.59703701628099</v>
       </c>
       <c r="F57">
-        <v>12.15944235632715</v>
+        <v>12.41780813937194</v>
       </c>
       <c r="G57">
-        <v>-3.590115639639894</v>
+        <v>-6.595322942733021</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.436645448748312</v>
       </c>
       <c r="E58">
-        <v>-15.46992138716665</v>
+        <v>-22.831653271632</v>
       </c>
       <c r="F58">
-        <v>12.51268954447183</v>
+        <v>12.57164458087998</v>
       </c>
       <c r="G58">
-        <v>-2.432801887839315</v>
+        <v>-7.654200933468911</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.352407444812358</v>
       </c>
       <c r="E59">
-        <v>-15.46200561460124</v>
+        <v>-19.70718281682575</v>
       </c>
       <c r="F59">
-        <v>12.20857524864774</v>
+        <v>12.68978587475994</v>
       </c>
       <c r="G59">
-        <v>-2.871435929610591</v>
+        <v>-7.266777720644621</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.271650506968479</v>
       </c>
       <c r="E60">
-        <v>-15.12520036028076</v>
+        <v>-20.31148503077932</v>
       </c>
       <c r="F60">
-        <v>12.54550234733382</v>
+        <v>12.18428436731673</v>
       </c>
       <c r="G60">
-        <v>-2.180736950479207</v>
+        <v>-7.073067769505246</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.192968485382282</v>
       </c>
       <c r="E61">
-        <v>-14.51608437845703</v>
+        <v>-19.41847901341474</v>
       </c>
       <c r="F61">
-        <v>12.27708003172599</v>
+        <v>12.59881622327118</v>
       </c>
       <c r="G61">
-        <v>-3.528575908610382</v>
+        <v>-7.583120210195219</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.11514060219984</v>
       </c>
       <c r="E62">
-        <v>-14.75500213862771</v>
+        <v>-19.60770129982524</v>
       </c>
       <c r="F62">
-        <v>12.66127916828203</v>
+        <v>12.60666823719993</v>
       </c>
       <c r="G62">
-        <v>-3.526834561656726</v>
+        <v>-6.568093705672515</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.036165465415377</v>
       </c>
       <c r="E63">
-        <v>-14.40334348956207</v>
+        <v>-19.26635851454908</v>
       </c>
       <c r="F63">
-        <v>12.26513255429992</v>
+        <v>13.11823375459335</v>
       </c>
       <c r="G63">
-        <v>-4.029461448702112</v>
+        <v>-7.753858285837591</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.956321396781236</v>
       </c>
       <c r="E64">
-        <v>-13.43293679445839</v>
+        <v>-17.61056274991048</v>
       </c>
       <c r="F64">
-        <v>12.50700087282358</v>
+        <v>12.82336988502134</v>
       </c>
       <c r="G64">
-        <v>-4.161846854272028</v>
+        <v>-7.674901774725973</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.876771478383318</v>
       </c>
       <c r="E65">
-        <v>-13.87694461396245</v>
+        <v>-20.34304396613877</v>
       </c>
       <c r="F65">
-        <v>12.50803186537453</v>
+        <v>12.22131933014929</v>
       </c>
       <c r="G65">
-        <v>-4.032487287325006</v>
+        <v>-7.588446877967906</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.798665200797116</v>
       </c>
       <c r="E66">
-        <v>-12.23189038967005</v>
+        <v>-17.32264690097681</v>
       </c>
       <c r="F66">
-        <v>11.8396889645881</v>
+        <v>12.64568758354452</v>
       </c>
       <c r="G66">
-        <v>-3.520938480051283</v>
+        <v>-7.94586992711532</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.722733708081784</v>
       </c>
       <c r="E67">
-        <v>-12.45212819455909</v>
+        <v>-17.78691058471718</v>
       </c>
       <c r="F67">
-        <v>12.16445478554952</v>
+        <v>12.22222204252109</v>
       </c>
       <c r="G67">
-        <v>-3.997455094428439</v>
+        <v>-8.94782639784898</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.650254620638448</v>
       </c>
       <c r="E68">
-        <v>-11.77984905727638</v>
+        <v>-15.7758333918068</v>
       </c>
       <c r="F68">
-        <v>12.58153640802782</v>
+        <v>12.63560412798092</v>
       </c>
       <c r="G68">
-        <v>-4.224452580965186</v>
+        <v>-8.572675377338768</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.583577980708385</v>
       </c>
       <c r="E69">
-        <v>-12.33240892721831</v>
+        <v>-16.53486450565445</v>
       </c>
       <c r="F69">
-        <v>12.1543903344569</v>
+        <v>12.5039981664079</v>
       </c>
       <c r="G69">
-        <v>-3.812809416975588</v>
+        <v>-8.901962099947918</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.525133609386112</v>
       </c>
       <c r="E70">
-        <v>-12.95036901877901</v>
+        <v>-16.23056010928702</v>
       </c>
       <c r="F70">
-        <v>12.09406855984373</v>
+        <v>12.86507044548077</v>
       </c>
       <c r="G70">
-        <v>-4.496440381380628</v>
+        <v>-7.778237143188784</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.475853825549954</v>
       </c>
       <c r="E71">
-        <v>-12.98642472882809</v>
+        <v>-17.41714256809486</v>
       </c>
       <c r="F71">
-        <v>12.00293895405751</v>
+        <v>12.12063681028114</v>
       </c>
       <c r="G71">
-        <v>-4.088644071307663</v>
+        <v>-9.386006894881374</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.435053691196193</v>
       </c>
       <c r="E72">
-        <v>-12.23756456760166</v>
+        <v>-17.3608989209196</v>
       </c>
       <c r="F72">
-        <v>12.50097645552125</v>
+        <v>12.23316069927903</v>
       </c>
       <c r="G72">
-        <v>-5.016109956862183</v>
+        <v>-8.432884281397504</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.402841735868153</v>
       </c>
       <c r="E73">
-        <v>-12.13014916413972</v>
+        <v>-14.89456517907011</v>
       </c>
       <c r="F73">
-        <v>12.20173839021079</v>
+        <v>12.09601176700197</v>
       </c>
       <c r="G73">
-        <v>-4.683390198528811</v>
+        <v>-9.481135420952333</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.378220780631167</v>
       </c>
       <c r="E74">
-        <v>-12.31921748243396</v>
+        <v>-16.92834814065494</v>
       </c>
       <c r="F74">
-        <v>11.88135626722331</v>
+        <v>11.96251486056592</v>
       </c>
       <c r="G74">
-        <v>-4.373639005146902</v>
+        <v>-8.010260037854144</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.358842524615155</v>
       </c>
       <c r="E75">
-        <v>-11.76708328904876</v>
+        <v>-14.27478464095832</v>
       </c>
       <c r="F75">
-        <v>11.63269543402833</v>
+        <v>11.8408070609644</v>
       </c>
       <c r="G75">
-        <v>-4.29425212311518</v>
+        <v>-7.384351745471838</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.340344987132098</v>
       </c>
       <c r="E76">
-        <v>-11.67168192712917</v>
+        <v>-16.13128237361687</v>
       </c>
       <c r="F76">
-        <v>11.53689072837973</v>
+        <v>11.95191036575613</v>
       </c>
       <c r="G76">
-        <v>-3.659114029769384</v>
+        <v>-8.785027010409781</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.320203037437448</v>
       </c>
       <c r="E77">
-        <v>-13.15757840394799</v>
+        <v>-17.144465034197</v>
       </c>
       <c r="F77">
-        <v>11.48609811225976</v>
+        <v>11.34097363699255</v>
       </c>
       <c r="G77">
-        <v>-4.759003058645765</v>
+        <v>-8.109715446944929</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.295865760126459</v>
       </c>
       <c r="E78">
-        <v>-12.91234795101061</v>
+        <v>-16.66038021972505</v>
       </c>
       <c r="F78">
-        <v>11.19224939817955</v>
+        <v>11.13336721224351</v>
       </c>
       <c r="G78">
-        <v>-3.934829504462046</v>
+        <v>-7.490964554018527</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.265779741089833</v>
       </c>
       <c r="E79">
-        <v>-12.32616869003574</v>
+        <v>-16.353345153531</v>
       </c>
       <c r="F79">
-        <v>10.97551607623983</v>
+        <v>11.64595421995239</v>
       </c>
       <c r="G79">
-        <v>-4.004629046612039</v>
+        <v>-7.375694668886643</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.229203697144219</v>
       </c>
       <c r="E80">
-        <v>-14.55888751477753</v>
+        <v>-20.01184043416578</v>
       </c>
       <c r="F80">
-        <v>11.45141336900572</v>
+        <v>11.39245199777391</v>
       </c>
       <c r="G80">
-        <v>-4.61121699522716</v>
+        <v>-7.219463403797358</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.18858708259357</v>
       </c>
       <c r="E81">
-        <v>-13.05995356129063</v>
+        <v>-17.42653915166078</v>
       </c>
       <c r="F81">
-        <v>11.16409585812078</v>
+        <v>11.68326158020239</v>
       </c>
       <c r="G81">
-        <v>-3.654333602010677</v>
+        <v>-7.473355762295143</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.148997012808542</v>
       </c>
       <c r="E82">
-        <v>-15.04434898534781</v>
+        <v>-17.90634455819547</v>
       </c>
       <c r="F82">
-        <v>10.86645575207901</v>
+        <v>10.72896949044196</v>
       </c>
       <c r="G82">
-        <v>-2.319306455116481</v>
+        <v>-6.656260154474386</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.117978444894841</v>
       </c>
       <c r="E83">
-        <v>-14.95810419787173</v>
+        <v>-16.13402662886551</v>
       </c>
       <c r="F83">
-        <v>10.93605645965074</v>
+        <v>10.84526735063634</v>
       </c>
       <c r="G83">
-        <v>-3.915267490870492</v>
+        <v>-7.345618362662364</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.103718397844195</v>
       </c>
       <c r="E84">
-        <v>-16.03107630077514</v>
+        <v>-17.58978611116329</v>
       </c>
       <c r="F84">
-        <v>11.07518660802801</v>
+        <v>10.45676053399031</v>
       </c>
       <c r="G84">
-        <v>-2.866933587677182</v>
+        <v>-6.280592688860049</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.114510132073871</v>
       </c>
       <c r="E85">
-        <v>-17.06468237912986</v>
+        <v>-21.08278378071375</v>
       </c>
       <c r="F85">
-        <v>11.0767449746488</v>
+        <v>10.76029044233161</v>
       </c>
       <c r="G85">
-        <v>-3.045249502058946</v>
+        <v>-6.723182832550753</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.158265978741423</v>
       </c>
       <c r="E86">
-        <v>-17.7213292241381</v>
+        <v>-20.39140806854069</v>
       </c>
       <c r="F86">
-        <v>10.90333234432001</v>
+        <v>10.61172774152198</v>
       </c>
       <c r="G86">
-        <v>-1.953179981746324</v>
+        <v>-7.210773221756771</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.24453175437844</v>
       </c>
       <c r="E87">
-        <v>-18.51465447164583</v>
+        <v>-21.79023557561403</v>
       </c>
       <c r="F87">
-        <v>10.6308905830988</v>
+        <v>10.68119541779682</v>
       </c>
       <c r="G87">
-        <v>-2.152567518485549</v>
+        <v>-5.957801256598951</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.379990219125776</v>
       </c>
       <c r="E88">
-        <v>-19.58415323498536</v>
+        <v>-22.90420395370888</v>
       </c>
       <c r="F88">
-        <v>10.41971448521636</v>
+        <v>9.862626924989545</v>
       </c>
       <c r="G88">
-        <v>-1.717892889179242</v>
+        <v>-6.144605409743406</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.56855056035197</v>
       </c>
       <c r="E89">
-        <v>-22.17900054069853</v>
+        <v>-25.07251429263958</v>
       </c>
       <c r="F89">
-        <v>10.51528163497763</v>
+        <v>10.62650688512486</v>
       </c>
       <c r="G89">
-        <v>-1.29646044203002</v>
+        <v>-4.135087714678099</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.80948653953072</v>
       </c>
       <c r="E90">
-        <v>-22.54335703088168</v>
+        <v>-25.86448099794502</v>
       </c>
       <c r="F90">
-        <v>9.726407628084852</v>
+        <v>9.900344465071651</v>
       </c>
       <c r="G90">
-        <v>-0.8920210251338767</v>
+        <v>-3.424730716134524</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.103887994156286</v>
       </c>
       <c r="E91">
-        <v>-23.48383051279466</v>
+        <v>-27.63717026214361</v>
       </c>
       <c r="F91">
-        <v>9.926955475568779</v>
+        <v>10.22257635656837</v>
       </c>
       <c r="G91">
-        <v>-0.2703502310418369</v>
+        <v>-4.537133607149349</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.447777657653154</v>
       </c>
       <c r="E92">
-        <v>-24.69877027583853</v>
+        <v>-28.57554253211703</v>
       </c>
       <c r="F92">
-        <v>9.47229567912893</v>
+        <v>9.605350731614575</v>
       </c>
       <c r="G92">
-        <v>-1.131595274174315</v>
+        <v>-3.819443750236288</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.833885267346132</v>
       </c>
       <c r="E93">
-        <v>-27.70244821496418</v>
+        <v>-29.83987662539957</v>
       </c>
       <c r="F93">
-        <v>9.087798805860794</v>
+        <v>9.430508014844145</v>
       </c>
       <c r="G93">
-        <v>-1.774559497174947</v>
+        <v>-3.140725635411527</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.249322784890957</v>
       </c>
       <c r="E94">
-        <v>-28.36212008060953</v>
+        <v>-32.47137739973082</v>
       </c>
       <c r="F94">
-        <v>9.344503281400291</v>
+        <v>8.602525974075501</v>
       </c>
       <c r="G94">
-        <v>-0.01219720043500897</v>
+        <v>-3.238833652467829</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.686449423655977</v>
       </c>
       <c r="E95">
-        <v>-29.24764958738745</v>
+        <v>-32.55821541730191</v>
       </c>
       <c r="F95">
-        <v>8.718220442316099</v>
+        <v>8.691872327000933</v>
       </c>
       <c r="G95">
-        <v>-0.000997624875654541</v>
+        <v>-3.957486878132818</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.137898306315692</v>
       </c>
       <c r="E96">
-        <v>-32.96373120774077</v>
+        <v>-35.84839632147084</v>
       </c>
       <c r="F96">
-        <v>8.237453253860231</v>
+        <v>7.539073786681574</v>
       </c>
       <c r="G96">
-        <v>0.6325878226122224</v>
+        <v>-1.909652928995986</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.58971895919021</v>
       </c>
       <c r="E97">
-        <v>-33.86200610461327</v>
+        <v>-37.93966826058305</v>
       </c>
       <c r="F97">
-        <v>7.391383707831353</v>
+        <v>6.923081868635908</v>
       </c>
       <c r="G97">
-        <v>0.2115228460178593</v>
+        <v>-2.685181327025655</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.038123305158289</v>
       </c>
       <c r="E98">
-        <v>-36.72164007826594</v>
+        <v>-36.95532292248375</v>
       </c>
       <c r="F98">
-        <v>7.740872761838699</v>
+        <v>7.513444673852018</v>
       </c>
       <c r="G98">
-        <v>0.7974000217392991</v>
+        <v>-1.736736514388774</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.466381724401429</v>
       </c>
       <c r="E99">
-        <v>-38.60529054107448</v>
+        <v>-41.60006776453805</v>
       </c>
       <c r="F99">
-        <v>7.004314896156544</v>
+        <v>6.835057910149868</v>
       </c>
       <c r="G99">
-        <v>1.96828701025089</v>
+        <v>-1.233914305156569</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.888199961442355</v>
       </c>
       <c r="E100">
-        <v>-41.25734153045254</v>
+        <v>-42.22564701361667</v>
       </c>
       <c r="F100">
-        <v>6.420788949377386</v>
+        <v>6.149888134011892</v>
       </c>
       <c r="G100">
-        <v>1.456761376795942</v>
+        <v>-2.714141979403199</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.26992461291719</v>
       </c>
       <c r="E101">
-        <v>-42.80215571834815</v>
+        <v>-45.35621732291124</v>
       </c>
       <c r="F101">
-        <v>5.920496250690065</v>
+        <v>5.814482976710549</v>
       </c>
       <c r="G101">
-        <v>0.8628164015952977</v>
+        <v>-2.114380375690056</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.654358024281739</v>
       </c>
       <c r="E102">
-        <v>-44.04383612040732</v>
+        <v>-49.39350926522113</v>
       </c>
       <c r="F102">
-        <v>6.190628968686572</v>
+        <v>5.243490478546179</v>
       </c>
       <c r="G102">
-        <v>1.061151184853035</v>
+        <v>-2.39794184331079</v>
       </c>
     </row>
   </sheetData>
